--- a/data/predictions/2026-03-25_HV.xlsx
+++ b/data/predictions/2026-03-25_HV.xlsx
@@ -539,12 +539,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -556,8 +560,10 @@
           <t>MANAGEMENT FOLKS</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -574,47 +580,79 @@
           <t>5/11/9/6/4/2</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.8289</v>
-      </c>
-      <c r="R2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.2</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.8289</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -626,8 +664,10 @@
           <t>KASA PAPA</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -644,47 +684,79 @@
           <t>10/9/7/2/7/4</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.5946</v>
-      </c>
-      <c r="R3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.5</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>9.28</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.5946</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -696,8 +768,10 @@
           <t>PERFECT PAIRING</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -714,47 +788,79 @@
           <t>3/12/6/8/2/5</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.5515</v>
-      </c>
-      <c r="R4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.8</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.5515</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -766,8 +872,10 @@
           <t>ROMANTIC FANTASY</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -784,47 +892,79 @@
           <t>2/2/2/8/4/10</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.4924</v>
-      </c>
-      <c r="R5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7.2</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>9.28</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.4924</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -836,8 +976,10 @@
           <t>RAGGA BOMB</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>7</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -854,47 +996,79 @@
           <t>3/1/8/2/8/5</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>10</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5.6007</v>
-      </c>
-      <c r="R6" t="n">
-        <v>14</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6.1</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5.6007</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -906,8 +1080,10 @@
           <t>YIU CHEUNG VICTORY</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>6</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -924,47 +1100,79 @@
           <t>8/7/13/1/7/1</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="R7" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7.5</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5.39</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -976,8 +1184,10 @@
           <t>TAKE ACTION</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>5</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -994,47 +1204,79 @@
           <t>8/2/2/5/11/3</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.3753</v>
-      </c>
-      <c r="R8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7.7</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5.3753</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1046,8 +1288,10 @@
           <t>TURIN WARRIOR</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>10</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1064,47 +1308,79 @@
           <t>4/6/12/3/1/6</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.3648</v>
-      </c>
-      <c r="R9" t="n">
-        <v>11</v>
-      </c>
-      <c r="S9" t="n">
-        <v>7.7</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.3648</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1116,8 +1392,10 @@
           <t>BITS SUPERSTAR</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>3</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1134,47 +1412,79 @@
           <t>2/2/2/3/7/2</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5.736842105263158</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.0275</v>
-      </c>
-      <c r="R10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.9</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5.736842105263158</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6.0275</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1186,8 +1496,10 @@
           <t>SUNNY Q</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1204,47 +1516,79 @@
           <t>9/5/6/5/2/1</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.842105263157895</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.7534</v>
-      </c>
-      <c r="R11" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5.1</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3.842105263157895</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5.7534</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1256,8 +1600,10 @@
           <t>A TIME FOR US</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>2</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1274,47 +1620,79 @@
           <t>13/8/8/4</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>10</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.271</v>
-      </c>
-      <c r="R12" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8.300000000000001</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5.271</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1326,8 +1704,10 @@
           <t>LEADING AGILITY</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>7</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1344,47 +1724,79 @@
           <t>9/7/3</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4.315789473684211</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.228</v>
-      </c>
-      <c r="R13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="S13" t="n">
-        <v>8.699999999999999</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4.315789473684211</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5.228</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1396,8 +1808,10 @@
           <t>GLORIOUS JOURNEY</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>2</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1414,47 +1828,79 @@
           <t>2/4/7/2/1/4</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.3182</v>
-      </c>
-      <c r="R14" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.8</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7.24</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6.3182</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1466,8 +1912,10 @@
           <t>FORTUNE STAR</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>5</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1484,47 +1932,79 @@
           <t>7/4/1/12/2/4</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>8.411764705882353</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.8185</v>
-      </c>
-      <c r="R15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.6</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>8.411764705882353</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5.8185</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1536,8 +2016,10 @@
           <t>BEAUTY VIVA</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1554,47 +2036,79 @@
           <t>9/5/9/2/7/7</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6.294117647058823</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.2223</v>
-      </c>
-      <c r="R16" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>8.300000000000001</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6.294117647058823</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5.2223</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1606,8 +2120,10 @@
           <t>DASHING PAL</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>10</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1624,47 +2140,79 @@
           <t>14/5</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6.294117647058823</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.8072</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>12.7</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6.294117647058823</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4.8072</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1676,8 +2224,10 @@
           <t>MR DESIRA</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>9</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1694,47 +2244,79 @@
           <t>12/4/1/3/1/2</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.647058823529412</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.0114</v>
-      </c>
-      <c r="R18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.6</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8.52</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.647058823529412</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6.0114</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1746,8 +2328,10 @@
           <t>CANDLELIGHT DINNER</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1764,47 +2348,79 @@
           <t>11/1/10/1/8/5</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>9.470588235294118</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.6714</v>
-      </c>
-      <c r="R19" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6.4</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>9.470588235294118</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5.6714</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1816,8 +2432,10 @@
           <t>BUNTA BABY</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>5</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1834,47 +2452,79 @@
           <t>1/3/1/2/3/8</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.4873</v>
-      </c>
-      <c r="R20" t="n">
-        <v>11</v>
-      </c>
-      <c r="S20" t="n">
-        <v>7.7</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5.4873</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1886,8 +2536,10 @@
           <t>TOGETHER WE VALUE</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>12</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1904,47 +2556,79 @@
           <t>7/8/2</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6.294117647058823</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.3042</v>
-      </c>
-      <c r="R21" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>9.300000000000001</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5.67</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>6.294117647058823</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5.3042</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1956,8 +2640,10 @@
           <t>DAN ATTACK</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>4</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1974,47 +2660,79 @@
           <t>5/2/3/1/4/1</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.2734</v>
-      </c>
-      <c r="R22" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.3</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>8.43</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6.2734</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2026,8 +2744,10 @@
           <t>KING PROFIT</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2044,47 +2764,79 @@
           <t>2/5/4/5/6/2</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="K23" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.9752</v>
-      </c>
-      <c r="R23" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.8</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>8.65</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5.9752</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2096,8 +2848,10 @@
           <t>SILVER SPURS</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>8</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2114,47 +2868,79 @@
           <t>9/3/9/3/1/2</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.9521</v>
-      </c>
-      <c r="R24" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>6</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>7.62</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5.9521</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2166,8 +2952,10 @@
           <t>GENIUS BABY</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>3</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2184,47 +2972,79 @@
           <t>2/9/4/4/1/5</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="K25" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.9024</v>
-      </c>
-      <c r="R25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>6.3</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5.9024</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2236,8 +3056,10 @@
           <t>VICTOR THE RAPID</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>3</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2254,47 +3076,79 @@
           <t>2/3/1/6/6/3</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="K26" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>10</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.1131</v>
-      </c>
-      <c r="R26" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6.1131</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2306,8 +3160,10 @@
           <t>GIANT BALLON</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>11</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2324,47 +3180,79 @@
           <t>1/5/3/4/2/8</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>9.526315789473685</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.6403</v>
-      </c>
-      <c r="R27" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6.3</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>9.526315789473685</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5.6403</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2376,8 +3264,10 @@
           <t>THE PERFECT MATCH</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>9</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2394,47 +3284,79 @@
           <t>7/4/3/2/2/9</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>7.157894736842105</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5.6328</v>
-      </c>
-      <c r="R28" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6.4</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>7.157894736842105</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5.6328</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2446,8 +3368,10 @@
           <t>PHOENIX LIGHT</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>10</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2464,47 +3388,79 @@
           <t>9/7/8/5/3/2</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>6.684210526315789</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.5149</v>
-      </c>
-      <c r="R29" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S29" t="n">
-        <v>7.2</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>6.684210526315789</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5.5149</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2516,8 +3472,10 @@
           <t>KING LOTUS</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2534,47 +3492,79 @@
           <t>11/11/4/2/2/3</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="K30" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.0067</v>
-      </c>
-      <c r="R30" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5.3</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>6.0067</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2586,8 +3576,10 @@
           <t>BEAUTY ALLIANCE</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>2</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2604,47 +3596,79 @@
           <t>2/7/5/5/8/3</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="K31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>10</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.7302</v>
-      </c>
-      <c r="R31" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5.7302</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2656,8 +3680,10 @@
           <t>WITHOUT COMPARE</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>12</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2674,47 +3700,79 @@
           <t>4/2/4/2</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.8125</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.7269</v>
-      </c>
-      <c r="R32" t="n">
-        <v>12</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7.1</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>3.8125</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5.7269</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2726,8 +3784,10 @@
           <t>SOLID WIN</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>6</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2744,47 +3804,79 @@
           <t>1/7/1/9/6/4</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>9.4375</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.5928</v>
-      </c>
-      <c r="R33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>8.1</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>9.4375</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5.5928</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2796,8 +3888,10 @@
           <t>CALIFORNIA BLITZ</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>12</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2814,47 +3908,79 @@
           <t>3/2/3/1/1/3</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.117647058823529</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.0002</v>
-      </c>
-      <c r="R34" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4.7</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>8.95</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>3.117647058823529</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>6.0002</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2866,8 +3992,10 @@
           <t>MY DAY MY WAY</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>10</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2884,47 +4012,79 @@
           <t>1/10/2/8/1/2</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="K35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>4.705882352941177</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>5.6816</v>
-      </c>
-      <c r="R35" t="n">
-        <v>13</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6.5</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>4.705882352941177</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>5.6816</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2936,8 +4096,10 @@
           <t>AMAZING KID</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>7</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2954,47 +4116,79 @@
           <t>1/7/1/1/1/11</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="K36" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4.705882352941177</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5.6557</v>
-      </c>
-      <c r="R36" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6.7</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>6.76</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>4.705882352941177</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>5.6557</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3006,8 +4200,10 @@
           <t>SYMBOL OF STRENGTH</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>4</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3024,39 +4220,67 @@
           <t>1/3/4/6/5/10</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="K37" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>10</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5.4404</v>
-      </c>
-      <c r="R37" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8.300000000000001</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>5.4404</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3235,7 +4459,6 @@
           <t>11/11/4/2/2/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.14</v>
       </c>
@@ -3316,7 +4539,6 @@
           <t>2/7/5/5/8/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.14</v>
       </c>
@@ -3397,7 +4619,6 @@
           <t>4/2/4/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.8</v>
       </c>
@@ -3478,7 +4699,6 @@
           <t>1/7/1/9/6/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.24</v>
       </c>
@@ -3559,7 +4779,6 @@
           <t>5/3/8/3/4/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>7.1</v>
       </c>
@@ -3640,7 +4859,6 @@
           <t>6/1/1/3/10/2</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>6.9</v>
       </c>
@@ -3721,7 +4939,6 @@
           <t>3/4/5/9/7/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.48</v>
       </c>
@@ -3802,7 +5019,6 @@
           <t>7/10/2/2/10/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.76</v>
       </c>
@@ -3883,7 +5099,6 @@
           <t>1/7/3/1/6/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5.05</v>
       </c>
@@ -3964,7 +5179,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5</v>
       </c>
@@ -4045,7 +5259,6 @@
           <t>8/12/9/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.2</v>
       </c>
@@ -4126,7 +5339,6 @@
           <t>14/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
       </c>
@@ -4338,7 +5550,6 @@
           <t>3/2/3/1/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.949999999999999</v>
       </c>
@@ -4419,7 +5630,6 @@
           <t>1/10/2/8/1/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.19</v>
       </c>
@@ -4500,7 +5710,6 @@
           <t>1/7/1/1/1/11</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.76</v>
       </c>
@@ -4581,7 +5790,6 @@
           <t>1/3/4/6/5/10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.33</v>
       </c>
@@ -4662,7 +5870,6 @@
           <t>1/2/4/10/5/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.86</v>
       </c>
@@ -4743,7 +5950,6 @@
           <t>4/7/1/4/6/10</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.38</v>
       </c>
@@ -4824,7 +6030,6 @@
           <t>7/3/10/1/7/6</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.81</v>
       </c>
@@ -4905,7 +6110,6 @@
           <t>5/1/8/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.9</v>
       </c>
@@ -4986,7 +6190,6 @@
           <t>1/4/3/14/8/8</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.43</v>
       </c>
@@ -5067,7 +6270,6 @@
           <t>10/5/7/8/8/7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.67</v>
       </c>
@@ -5233,7 +6435,6 @@
           <t>8/1/11/13/12/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.19</v>
       </c>
@@ -5418,7 +6619,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>2</t>
@@ -5520,7 +6720,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>1</t>
@@ -5622,7 +6821,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>6</t>
@@ -5724,7 +6922,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>1</t>
@@ -5826,7 +7023,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>8</t>
@@ -5928,7 +7124,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>8</t>
@@ -6030,7 +7225,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -6132,7 +7326,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>6</t>
@@ -6234,7 +7427,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>8</t>
@@ -6509,7 +7701,6 @@
           <t>5/11/9/6/4/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.38</v>
       </c>
@@ -6590,7 +7781,6 @@
           <t>10/9/7/2/7/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>4.81</v>
       </c>
@@ -6671,7 +7861,6 @@
           <t>3/12/6/8/2/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -6752,7 +7941,6 @@
           <t>2/2/2/8/4/10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.67</v>
       </c>
@@ -6833,7 +8021,6 @@
           <t>1/2/6/1/8/9</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.86</v>
       </c>
@@ -6999,7 +8186,6 @@
           <t>9/10/7/9/6/6</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.1</v>
       </c>
@@ -7080,7 +8266,6 @@
           <t>2/3/8/10/4/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.38</v>
       </c>
@@ -7161,7 +8346,6 @@
           <t>4/6/5/9/8/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.52</v>
       </c>
@@ -7242,7 +8426,6 @@
           <t>12/11/11/12/7/13</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.48</v>
       </c>
@@ -7323,7 +8506,6 @@
           <t>13/13/7/7/4/8</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>3.14</v>
       </c>
@@ -7404,7 +8586,6 @@
           <t>9/9/11/10/8/13</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.38</v>
       </c>
@@ -7616,7 +8797,6 @@
           <t>3/1/8/2/8/5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.24</v>
       </c>
@@ -7697,7 +8877,6 @@
           <t>8/7/13/1/7/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6</v>
       </c>
@@ -7778,7 +8957,6 @@
           <t>8/2/2/5/11/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.71</v>
       </c>
@@ -7859,7 +9037,6 @@
           <t>4/6/12/3/1/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.86</v>
       </c>
@@ -7940,7 +9117,6 @@
           <t>1/8/11/7/1/7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.62</v>
       </c>
@@ -8021,7 +9197,6 @@
           <t>7/10/5/1/7/3</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.86</v>
       </c>
@@ -8102,7 +9277,6 @@
           <t>10/3/3/3/4/9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.48</v>
       </c>
@@ -8183,7 +9357,6 @@
           <t>11/3/11/4/4/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.81</v>
       </c>
@@ -8264,7 +9437,6 @@
           <t>10/5/12/10/3/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.05</v>
       </c>
@@ -8345,7 +9517,6 @@
           <t>12/10/13/12/12/14</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1</v>
       </c>
@@ -8426,7 +9597,6 @@
           <t>5/12/8/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.1</v>
       </c>
@@ -8507,7 +9677,6 @@
           <t>9/3/8/12/8/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.1</v>
       </c>
@@ -8719,7 +9888,6 @@
           <t>2/2/2/3/7/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.38</v>
       </c>
@@ -8800,7 +9968,6 @@
           <t>9/5/6/5/2/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.1</v>
       </c>
@@ -8881,7 +10048,6 @@
           <t>13/8/8/4</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>3.5</v>
       </c>
@@ -8962,7 +10128,6 @@
           <t>9/7/3</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.33</v>
       </c>
@@ -9043,7 +10208,6 @@
           <t>3/3/8/4/6/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.1</v>
       </c>
@@ -9124,7 +10288,6 @@
           <t>3/8/13/8/6/13</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2.33</v>
       </c>
@@ -9205,7 +10368,6 @@
           <t>8/11/5/2/11/8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.43</v>
       </c>
@@ -9286,7 +10448,6 @@
           <t>1/9/8/9/12/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1.86</v>
       </c>
@@ -9367,7 +10528,6 @@
           <t>6/14/9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2</v>
       </c>
@@ -9448,7 +10608,6 @@
           <t>7/14/12/11/3/8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.05</v>
       </c>
@@ -9529,7 +10688,6 @@
           <t>11/12/12/11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -9610,7 +10768,6 @@
           <t>9/8/6/8/11/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.05</v>
       </c>
@@ -9822,7 +10979,6 @@
           <t>2/4/7/2/1/4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.24</v>
       </c>
@@ -9903,7 +11059,6 @@
           <t>7/4/1/12/2/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.19</v>
       </c>
@@ -9984,7 +11139,6 @@
           <t>9/5/9/2/7/7</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.14</v>
       </c>
@@ -10065,7 +11219,6 @@
           <t>14/5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>3.67</v>
       </c>
@@ -10146,7 +11299,6 @@
           <t>9/6/11/6/6/11</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2.62</v>
       </c>
@@ -10227,7 +11379,6 @@
           <t>1/7/10/3/4/10</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.14</v>
       </c>
@@ -10308,7 +11459,6 @@
           <t>2/14/12/8/10</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>1.8</v>
       </c>
@@ -10389,7 +11539,6 @@
           <t>5/7/10/9/9/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1.81</v>
       </c>
@@ -10470,7 +11619,6 @@
           <t>11/12/12/13/12/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1</v>
       </c>
@@ -10551,7 +11699,6 @@
           <t>8/6/11/12/13</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.47</v>
       </c>
@@ -10632,7 +11779,6 @@
           <t>7/8/10/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.4</v>
       </c>
@@ -10713,7 +11859,6 @@
           <t>12/12/6/14/10/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.43</v>
       </c>
@@ -10925,7 +12070,6 @@
           <t>12/4/1/3/1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.52</v>
       </c>
@@ -11006,7 +12150,6 @@
           <t>11/1/10/1/8/5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>4.95</v>
       </c>
@@ -11087,7 +12230,6 @@
           <t>1/3/1/2/3/8</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.86</v>
       </c>
@@ -11168,7 +12310,6 @@
           <t>7/8/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.67</v>
       </c>
@@ -11249,7 +12390,6 @@
           <t>9/6/4/13/5/5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.14</v>
       </c>
@@ -11330,7 +12470,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -11411,7 +12550,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -11492,7 +12630,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -11573,7 +12710,6 @@
           <t>10/6/6/8/9/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.14</v>
       </c>
@@ -11654,7 +12790,6 @@
           <t>8/5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>4</v>
       </c>
@@ -11735,7 +12870,6 @@
           <t>5/9/5/9/11/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.33</v>
       </c>
@@ -11816,7 +12950,6 @@
           <t>10/8/11/9/13/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.29</v>
       </c>
@@ -12028,7 +13161,6 @@
           <t>5/2/3/1/4/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.43</v>
       </c>
@@ -12109,7 +13241,6 @@
           <t>2/5/4/5/6/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.24</v>
       </c>
@@ -12190,7 +13321,6 @@
           <t>9/3/9/3/1/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.62</v>
       </c>
@@ -12271,7 +13401,6 @@
           <t>2/9/4/4/1/5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.43</v>
       </c>
@@ -12352,7 +13481,6 @@
           <t>11/7/11/10/3/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.43</v>
       </c>
@@ -12433,7 +13561,6 @@
           <t>8/4/12/1/4/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.57</v>
       </c>
@@ -12514,7 +13641,6 @@
           <t>5/3/7/9/9/7</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.14</v>
       </c>
@@ -12595,7 +13721,6 @@
           <t>11/14/2/9/5/7</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.86</v>
       </c>
@@ -12761,7 +13886,6 @@
           <t>9/13/8/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.4</v>
       </c>
@@ -13143,7 +14267,6 @@
           <t>2/3/1/6/6/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.62</v>
       </c>
@@ -13224,7 +14347,6 @@
           <t>1/5/3/4/2/8</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.95</v>
       </c>
@@ -13305,7 +14427,6 @@
           <t>7/4/3/2/2/9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.29</v>
       </c>
@@ -13386,7 +14507,6 @@
           <t>9/7/8/5/3/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.1</v>
       </c>
@@ -13467,7 +14587,6 @@
           <t>11/3/5/5/7/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.48</v>
       </c>
@@ -13633,7 +14752,6 @@
           <t>7/5/8/9/7/5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.43</v>
       </c>
@@ -13714,7 +14832,6 @@
           <t>2/7/7/11/8/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.1</v>
       </c>
@@ -13795,7 +14912,6 @@
           <t>9/11/12/11/14/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
@@ -13876,7 +14992,6 @@
           <t>11/8/4/12/10/7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.38</v>
       </c>
@@ -13957,7 +15072,6 @@
           <t>8/14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.33</v>
       </c>
@@ -14038,7 +15152,6 @@
           <t>12/6/11/12/12/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.29</v>
       </c>
